--- a/employment_forms/021_recruitment_submission_form--employment_forms.xlsx
+++ b/employment_forms/021_recruitment_submission_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>work_status</t>
+          <t>work_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Work Status</t>
+          <t>Work Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_description_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Job Description 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>work_experience</t>
+          <t>work_experience_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Work Experience</t>
+          <t>Work Experience 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>notice_period</t>
+          <t>notice_period_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Notice Period</t>
+          <t>Notice Period 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_3_months',_'value':_'less_than_3_months'}</t>
+          <t>less_than_3_months</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 3 months', 'value': 'less_than_3_months'}</t>
+          <t>Less than 3 months</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3_to_6_months',_'value':_'three_to_six_months'}</t>
+          <t>3_to_6_months</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3 to 6 months', 'value': 'three_to_six_months'}</t>
+          <t>3 to 6 months</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'6_months_to_1_year',_'value':_'six_months_to_one_year'}</t>
+          <t>6_months_to_1_year</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '6 months to 1 year', 'value': 'six_months_to_one_year'}</t>
+          <t>6 months to 1 year</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'1_to_2_years',_'value':_'one_to_two_years'}</t>
+          <t>1_to_2_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '1 to 2 years', 'value': 'one_to_two_years'}</t>
+          <t>1 to 2 years</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'2_years_or_more',_'value':_'two_or_more_years'}</t>
+          <t>2_years_or_more</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '2 years or more', 'value': 'two_or_more_years'}</t>
+          <t>2 years or more</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Part-time', 'value': 'part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Full-time', 'value': 'full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'contract',_'value':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Contract', 'value': 'contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'freelance',_'value':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Freelance', 'value': 'freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_(please_specify)',_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other (please specify)', 'value': 'other'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'permanent',_'value':_'permanent'}</t>
+          <t>permanent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Permanent', 'value': 'permanent'}</t>
+          <t>Permanent</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'temporary',_'value':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Temporary', 'value': 'temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'seasonal',_'value':_'seasonal'}</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Seasonal', 'value': 'seasonal'}</t>
+          <t>Seasonal</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'intern',_'value':_'intern'}</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Intern', 'value': 'intern'}</t>
+          <t>Intern</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_(please_specify)',_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other (please specify)', 'value': 'other'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full-time', 'value': 'full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part-time', 'value': 'part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'permanent',_'value':_'permanent'}</t>
+          <t>permanent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Permanent', 'value': 'permanent'}</t>
+          <t>Permanent</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'temporary',_'value':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Temporary', 'value': 'temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'remote',_'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Remote', 'value': 'remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'on-site',_'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'On-site', 'value': 'on-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid', 'value': 'hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'entry-level',_'value':_'entry-level'}</t>
+          <t>entry-level</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Entry-Level', 'value': 'entry-level'}</t>
+          <t>Entry-Level</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mid-level',_'value':_'mid-level'}</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mid-Level', 'value': 'mid-level'}</t>
+          <t>Mid-Level</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'senior',_'value':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Senior', 'value': 'senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'executive',_'value':_'executive'}</t>
+          <t>executive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Executive', 'value': 'executive'}</t>
+          <t>Executive</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Approved', 'value': 'approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rejected',_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rejected', 'value': 'rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
